--- a/CNN_Metrics.xlsx
+++ b/CNN_Metrics.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="28" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="42" uniqueCount="14">
   <si>
     <t>Class</t>
   </si>
@@ -156,13 +156,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>0.10000000000000001</v>
+        <v>0</v>
       </c>
       <c r="C4" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="0">
-        <v>0.18181818181818177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -226,13 +226,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>0</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="C9" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="0">
-        <v>0</v>
+        <v>0.18181818181818177</v>
       </c>
     </row>
     <row r="10">
